--- a/students.xlsx
+++ b/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TCS\Downloads\noname_sas1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\II-II\COMP 207 COMPUTER PROJECT II\Smart-Attendance-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0376457B-EA18-42ED-B616-415E3297E57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5964BA-67A7-4682-9CC5-71A0A7C9C48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1545" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>student_id</t>
   </si>
@@ -129,61 +118,13 @@
   </si>
   <si>
     <t>koishna123</t>
-  </si>
-  <si>
-    <t>SUSECE250001</t>
-  </si>
-  <si>
-    <t>Pranav Karki</t>
-  </si>
-  <si>
-    <t>pranav.karki@student.ku.edu.np</t>
-  </si>
-  <si>
-    <t>pranav123</t>
-  </si>
-  <si>
-    <t>SUSECE250002</t>
-  </si>
-  <si>
-    <t>Riya Tamang</t>
-  </si>
-  <si>
-    <t>riya.tamang@student.ku.edu.np</t>
-  </si>
-  <si>
-    <t>riya123</t>
-  </si>
-  <si>
-    <t>SUSECE250003</t>
-  </si>
-  <si>
-    <t>Samrat Gurung</t>
-  </si>
-  <si>
-    <t>samrat.gurung@student.ku.edu.np</t>
-  </si>
-  <si>
-    <t>samrat123</t>
-  </si>
-  <si>
-    <t>SUSECE250004</t>
-  </si>
-  <si>
-    <t>Tara Bista</t>
-  </si>
-  <si>
-    <t>tara.bista@student.ku.edu.np</t>
-  </si>
-  <si>
-    <t>tara123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,8 +477,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.42578125" customWidth="1"/>
@@ -545,7 +486,7 @@
     <col min="6" max="6" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -585,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -605,7 +546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -625,7 +566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -645,7 +586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -665,7 +606,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -683,86 +624,6 @@
       </c>
       <c r="F7" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
